--- a/data/raw/essai donnees paye.xlsx
+++ b/data/raw/essai donnees paye.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Morta\OneDrive\Desktop\Gam3a\MARS\Integrated Project\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C043E85B-7C9B-46AD-B78B-8F0F15ED9141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD967295-746F-408E-97C2-AF16356BCA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7A52D68B-53E4-4AF1-9470-D388864CCDDD}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15623" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15626" uniqueCount="207">
   <si>
     <t>Récapitulatif de paie détaillé - Juillet 2025</t>
   </si>
@@ -661,6 +661,12 @@
   <si>
     <t>net_imposable</t>
   </si>
+  <si>
+    <t>+::Salaire Brut::label;;+::Salaire de base::label</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
 </sst>
 </file>
 
@@ -10664,10 +10670,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -10684,6 +10686,10 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20169,10 +20175,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -20189,6 +20191,10 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30748,10 +30754,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -30768,6 +30770,10 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30775,7 +30781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEF3AD5-1AD6-4817-AF2D-AFF93B4D648F}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -30819,7 +30825,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -30852,6 +30858,17 @@
         <v>195</v>
       </c>
       <c r="C7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -46004,9 +46021,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
@@ -46023,6 +46037,9 @@
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -54012,9 +54029,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BD1"/>
     <mergeCell ref="C3:E3"/>
@@ -54031,6 +54045,9 @@
     <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -63380,9 +63397,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BD1"/>
     <mergeCell ref="C3:E3"/>
@@ -63399,6 +63413,9 @@
     <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/essai donnees paye.xlsx
+++ b/data/raw/essai donnees paye.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Morta\OneDrive\Desktop\Gam3a\MARS\Integrated Project\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD967295-746F-408E-97C2-AF16356BCA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E15715F-59E5-4085-97C2-D6CBDB69EC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7A52D68B-53E4-4AF1-9470-D388864CCDDD}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15626" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15626" uniqueCount="209">
   <si>
     <t>Récapitulatif de paie détaillé - Juillet 2025</t>
   </si>
@@ -647,25 +647,31 @@
     <t>cot_salariale</t>
   </si>
   <si>
-    <t>+::Salaire de base::label</t>
-  </si>
-  <si>
     <t>total_cost</t>
   </si>
   <si>
     <t>cot_patronale</t>
   </si>
   <si>
-    <t>-::Salaire Brut::label;;-::Salaire de base::label</t>
-  </si>
-  <si>
     <t>net_imposable</t>
   </si>
   <si>
-    <t>+::Salaire Brut::label;;+::Salaire de base::label</t>
+    <t>+::Total des retenues::label</t>
   </si>
   <si>
-    <t>test</t>
+    <t>+::Coût global::label</t>
+  </si>
+  <si>
+    <t>+::Coût global::label;;-::Salaire Brut::label</t>
+  </si>
+  <si>
+    <t>-::Net à payer::label</t>
+  </si>
+  <si>
+    <t>net_paye</t>
+  </si>
+  <si>
+    <t>+::Net à payer::label</t>
   </si>
 </sst>
 </file>
@@ -10670,6 +10676,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -10682,14 +10696,6 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20175,6 +20181,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -20187,14 +20201,6 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30754,6 +30760,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BG1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -30766,14 +30780,6 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30825,51 +30831,51 @@
         <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
         <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B6" t="s">
         <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B7" t="s">
         <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
         <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -46021,8 +46027,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BD1"/>
     <mergeCell ref="C3:E3"/>
@@ -46040,6 +46044,8 @@
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -54029,6 +54035,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BD1"/>
     <mergeCell ref="C3:E3"/>
@@ -54042,12 +54054,6 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -63397,6 +63403,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="A1:BD1"/>
     <mergeCell ref="C3:E3"/>
@@ -63410,12 +63422,6 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
